--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260708.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260708.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>34,140</t>
+          <t>33,804</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.03%</t>
+          <t>10.97%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>82,522</t>
+          <t>81,710</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.80%</t>
+          <t>9.89%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>95,188</t>
+          <t>94,251</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.73%</t>
+          <t>9.07%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>37,469</t>
+          <t>37,100</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.38%</t>
+          <t>7.49%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>205,662</t>
+          <t>203,636</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.46%</t>
+          <t>5.39%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>109,379</t>
+          <t>108,302</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>4.16%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>51,633</t>
+          <t>51,124</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>3.94%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>118,626</t>
+          <t>117,458</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.43%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>20,423</t>
+          <t>20,221</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>62,133</t>
+          <t>61,521</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>123,386</t>
+          <t>122,171</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>57,147</t>
+          <t>56,584</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
@@ -875,56 +875,56 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>143,639</t>
+          <t>142,224</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>FSLR US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>第一太陽能</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>25,612</t>
+          <t>23,510</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>FSLR US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>第一太陽能</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>23,744</t>
+          <t>25,360</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -941,56 +941,56 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>65,657</t>
+          <t>65,010</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>38,760</t>
+          <t>11,830</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>11,947</t>
+          <t>38,378</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>52,414</t>
+          <t>51,898</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>53,967</t>
+          <t>53,435</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1051,56 +1051,56 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>34,261</t>
+          <t>33,923</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>81,147</t>
+          <t>52,236</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>52,755</t>
+          <t>80,347</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>32,084</t>
+          <t>31,768</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>23,457</t>
+          <t>23,226</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>5,186</t>
+          <t>5,135</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>49,559</t>
+          <t>49,071</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,44 +1195,44 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>21,824</t>
+          <t>28,767</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>29,053</t>
+          <t>21,609</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>100,181</t>
+          <t>99,194</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1271,29 +1271,29 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>79,116</t>
+          <t>78,337</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>31,946</t>
+          <t>9,396</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1315,29 +1315,29 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>13,966</t>
+          <t>13,828</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>9,489</t>
+          <t>31,632</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>11,219</t>
+          <t>11,109</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>153,802</t>
+          <t>152,287</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>32,343</t>
+          <t>32,025</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>27,169</t>
+          <t>26,901</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>45,824</t>
+          <t>45,373</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>14,146</t>
+          <t>14,007</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>16,995</t>
+          <t>16,828</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>7,195</t>
+          <t>7,124</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>6,194</t>
+          <t>6,133</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>3,848</t>
+          <t>3,810</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>99,589</t>
+          <t>98,609</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>24,785</t>
+          <t>24,541</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,992</t>
+          <t>2,963</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,453</t>
+          <t>8,370</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>19,446</t>
+          <t>19,254</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>40,321</t>
+          <t>39,924</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>126,481,657</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
